--- a/artfynd/A 10455-2024 artfynd.xlsx
+++ b/artfynd/A 10455-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>84176410</v>
+        <v>84176417</v>
       </c>
       <c r="B2" t="n">
-        <v>55834</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57890</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100091</v>
+        <v>100082</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Storspov</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Numenius arquata</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>421030.5544226954</v>
+        <v>421031</v>
       </c>
       <c r="R2" t="n">
-        <v>6455879.171850501</v>
+        <v>6455879</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -760,19 +755,9 @@
           <t>2020-04-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-04-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,6 +781,115 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>84176410</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57340</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100091</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Storspov</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Numenius arquata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Gamla ån, Storegården, Valtorp, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>421031</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6455879</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Valtorp</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2020-04-04</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2020-04-04</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mikael Svensson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mikael Svensson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
